--- a/front-end/docs/wqm_stations.xlsx
+++ b/front-end/docs/wqm_stations.xlsx
@@ -5,18 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlfonsoSabalbosa\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EMBR3 WATER QUALITY MONITORING\water-quality-monitoring\front-end\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC6B32AB-9BBB-4682-83E2-391016E17210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66005E4D-719C-4E80-862A-F51AEDA993FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6450" yWindow="2625" windowWidth="18390" windowHeight="16050" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1680" yWindow="6165" windowWidth="30840" windowHeight="16050" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Station_List" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Station_List!$A$1:$G$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Station_List!$A$1:$G$95</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="288">
   <si>
     <t>ID</t>
   </si>
@@ -68,9 +68,6 @@
     <t>Bridge near Public Market (UBVAS)</t>
   </si>
   <si>
-    <t>BOCAUE</t>
-  </si>
-  <si>
     <t>Binang_1st</t>
   </si>
   <si>
@@ -834,6 +831,78 @@
   </si>
   <si>
     <t xml:space="preserve">Up-stream </t>
+  </si>
+  <si>
+    <t>Waterbody</t>
+  </si>
+  <si>
+    <t>Talisay River</t>
+  </si>
+  <si>
+    <t>Pampanga River</t>
+  </si>
+  <si>
+    <t>Angat River</t>
+  </si>
+  <si>
+    <t>Santa Maria River</t>
+  </si>
+  <si>
+    <t>Marilao River</t>
+  </si>
+  <si>
+    <t>Meycauayan River</t>
+  </si>
+  <si>
+    <t>Bagsit River</t>
+  </si>
+  <si>
+    <t>Dicaloyungan River</t>
+  </si>
+  <si>
+    <t>Talavera River</t>
+  </si>
+  <si>
+    <t>Baler Bay</t>
+  </si>
+  <si>
+    <t>Zambales Bay</t>
+  </si>
+  <si>
+    <t>Nagbalayong Bay</t>
+  </si>
+  <si>
+    <t>Montemar Beach</t>
+  </si>
+  <si>
+    <t>Subic Bay</t>
+  </si>
+  <si>
+    <t>Sasmuan River</t>
+  </si>
+  <si>
+    <t>Mexico River</t>
+  </si>
+  <si>
+    <t>San Fernando River</t>
+  </si>
+  <si>
+    <t>Abacan River</t>
+  </si>
+  <si>
+    <t>Talisay Mouth</t>
+  </si>
+  <si>
+    <t>Guagua River</t>
+  </si>
+  <si>
+    <t>Hagonoy River</t>
+  </si>
+  <si>
+    <t>Malolos River</t>
+  </si>
+  <si>
+    <t>Baler River</t>
   </si>
 </sst>
 </file>
@@ -907,7 +976,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -928,6 +997,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1262,7 +1334,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:H95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="34.875" customWidth="1"/>
@@ -1271,9 +1343,10 @@
     <col min="5" max="5" width="18.25" style="3" customWidth="1"/>
     <col min="6" max="6" width="26.125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.75" customWidth="1"/>
+    <col min="8" max="8" width="31.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1295,8 +1368,11 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -1310,21 +1386,24 @@
         <v>14.798365209</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>10</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
       </c>
       <c r="C3">
         <v>120.92749868200001</v>
@@ -1333,21 +1412,24 @@
         <v>14.795589076000001</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>14</v>
       </c>
-      <c r="G3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
       </c>
       <c r="C4">
         <v>120.93746690499999</v>
@@ -1356,21 +1438,24 @@
         <v>14.810743286999999</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" t="s">
         <v>9</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>10</v>
       </c>
-      <c r="G4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H4" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
         <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
       </c>
       <c r="C5">
         <v>120.558741846</v>
@@ -1379,21 +1464,24 @@
         <v>14.689782168000001</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" t="s">
         <v>19</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>20</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
         <v>22</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
       </c>
       <c r="C6">
         <v>120.54439232999999</v>
@@ -1402,21 +1490,24 @@
         <v>14.676776718999999</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>24</v>
       </c>
-      <c r="G6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
         <v>25</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
       </c>
       <c r="C7">
         <v>120.53593886500001</v>
@@ -1425,21 +1516,24 @@
         <v>14.651869835999999</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>27</v>
       </c>
-      <c r="G7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
         <v>28</v>
-      </c>
-      <c r="B8" t="s">
-        <v>29</v>
       </c>
       <c r="C8">
         <v>120.72298068000001</v>
@@ -1448,21 +1542,24 @@
         <v>14.893085622999999</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" t="s">
         <v>30</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>31</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
         <v>33</v>
-      </c>
-      <c r="B9" t="s">
-        <v>34</v>
       </c>
       <c r="C9">
         <v>120.73058650599999</v>
@@ -1471,21 +1568,24 @@
         <v>14.899395276</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>35</v>
       </c>
-      <c r="G9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
         <v>36</v>
-      </c>
-      <c r="B10" t="s">
-        <v>37</v>
       </c>
       <c r="C10">
         <v>120.76570502600001</v>
@@ -1494,21 +1594,24 @@
         <v>14.919912881</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="H10" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" t="s">
         <v>38</v>
-      </c>
-      <c r="B11" t="s">
-        <v>39</v>
       </c>
       <c r="C11">
         <v>120.758607025</v>
@@ -1517,21 +1620,24 @@
         <v>14.934689827</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>40</v>
       </c>
-      <c r="G11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>41</v>
-      </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C12">
         <v>120.77663638</v>
@@ -1540,21 +1646,24 @@
         <v>14.954248227000001</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F12" t="s">
+        <v>41</v>
+      </c>
+      <c r="G12" t="s">
+        <v>31</v>
+      </c>
+      <c r="H12" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>42</v>
       </c>
-      <c r="G12" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="B13" t="s">
         <v>43</v>
-      </c>
-      <c r="B13" t="s">
-        <v>44</v>
       </c>
       <c r="C13">
         <v>120.76717499999999</v>
@@ -1563,21 +1672,24 @@
         <v>14.867922</v>
       </c>
       <c r="E13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" t="s">
         <v>45</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>46</v>
       </c>
-      <c r="G13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="B14" t="s">
         <v>47</v>
-      </c>
-      <c r="B14" t="s">
-        <v>48</v>
       </c>
       <c r="C14">
         <v>120.762735615</v>
@@ -1586,21 +1698,24 @@
         <v>14.878281300999999</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F14" t="s">
+        <v>48</v>
+      </c>
+      <c r="G14" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>49</v>
       </c>
-      <c r="G14" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="B15" t="s">
         <v>50</v>
-      </c>
-      <c r="B15" t="s">
-        <v>51</v>
       </c>
       <c r="C15">
         <v>120.77190257399999</v>
@@ -1609,21 +1724,24 @@
         <v>14.901338183</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F15" t="s">
+        <v>51</v>
+      </c>
+      <c r="G15" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>52</v>
       </c>
-      <c r="G15" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="B16" t="s">
         <v>53</v>
-      </c>
-      <c r="B16" t="s">
-        <v>54</v>
       </c>
       <c r="C16">
         <v>121.02242</v>
@@ -1632,21 +1750,24 @@
         <v>14.9396</v>
       </c>
       <c r="E16" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F16" t="s">
         <v>55</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
+        <v>10</v>
+      </c>
+      <c r="H16" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>56</v>
       </c>
-      <c r="G16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="B17" t="s">
         <v>57</v>
-      </c>
-      <c r="B17" t="s">
-        <v>58</v>
       </c>
       <c r="C17">
         <v>121.03136000000001</v>
@@ -1655,21 +1776,24 @@
         <v>14.92426</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F17" t="s">
+        <v>58</v>
+      </c>
+      <c r="G17" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>59</v>
       </c>
-      <c r="G17" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="B18" t="s">
         <v>60</v>
-      </c>
-      <c r="B18" t="s">
-        <v>61</v>
       </c>
       <c r="C18">
         <v>121.03028</v>
@@ -1678,21 +1802,24 @@
         <v>14.91724</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F18" t="s">
+        <v>61</v>
+      </c>
+      <c r="G18" t="s">
+        <v>10</v>
+      </c>
+      <c r="H18" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>62</v>
       </c>
-      <c r="G18" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="B19" t="s">
         <v>63</v>
-      </c>
-      <c r="B19" t="s">
-        <v>64</v>
       </c>
       <c r="C19">
         <v>120.94942818600001</v>
@@ -1701,21 +1828,24 @@
         <v>14.817724146</v>
       </c>
       <c r="E19" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F19" t="s">
         <v>65</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>66</v>
       </c>
-      <c r="G19" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="B20" t="s">
         <v>67</v>
-      </c>
-      <c r="B20" t="s">
-        <v>68</v>
       </c>
       <c r="C20">
         <v>120.958738715</v>
@@ -1724,21 +1854,24 @@
         <v>14.817447109</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H20" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" t="s">
         <v>69</v>
-      </c>
-      <c r="B21" t="s">
-        <v>70</v>
       </c>
       <c r="C21">
         <v>120.988809135</v>
@@ -1747,21 +1880,24 @@
         <v>14.826400043</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F21" t="s">
+        <v>70</v>
+      </c>
+      <c r="G21" t="s">
+        <v>10</v>
+      </c>
+      <c r="H21" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>71</v>
       </c>
-      <c r="G21" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="B22" t="s">
         <v>72</v>
-      </c>
-      <c r="B22" t="s">
-        <v>73</v>
       </c>
       <c r="C22">
         <v>120.95101099999999</v>
@@ -1770,21 +1906,24 @@
         <v>14.754350000000001</v>
       </c>
       <c r="E22" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F22" t="s">
         <v>74</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
+        <v>10</v>
+      </c>
+      <c r="H22" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>75</v>
       </c>
-      <c r="G22" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="B23" t="s">
         <v>76</v>
-      </c>
-      <c r="B23" t="s">
-        <v>77</v>
       </c>
       <c r="C23">
         <v>120.99146231100001</v>
@@ -1793,21 +1932,24 @@
         <v>14.777684953</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F23" t="s">
+        <v>77</v>
+      </c>
+      <c r="G23" t="s">
+        <v>10</v>
+      </c>
+      <c r="H23" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>78</v>
       </c>
-      <c r="G23" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>79</v>
-      </c>
       <c r="B24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C24">
         <v>120.958769</v>
@@ -1816,21 +1958,24 @@
         <v>14.771083000000001</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F24" t="s">
+        <v>79</v>
+      </c>
+      <c r="G24" t="s">
+        <v>10</v>
+      </c>
+      <c r="H24" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>80</v>
       </c>
-      <c r="G24" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="B25" t="s">
         <v>81</v>
-      </c>
-      <c r="B25" t="s">
-        <v>82</v>
       </c>
       <c r="C25">
         <v>121.02701894800001</v>
@@ -1839,21 +1984,24 @@
         <v>14.77962838</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F25" t="s">
+        <v>82</v>
+      </c>
+      <c r="G25" t="s">
+        <v>10</v>
+      </c>
+      <c r="H25" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>83</v>
       </c>
-      <c r="G25" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="B26" t="s">
         <v>84</v>
-      </c>
-      <c r="B26" t="s">
-        <v>85</v>
       </c>
       <c r="C26">
         <v>120.949747</v>
@@ -1862,21 +2010,24 @@
         <v>14.760643999999999</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F26" t="s">
+        <v>85</v>
+      </c>
+      <c r="G26" t="s">
+        <v>10</v>
+      </c>
+      <c r="H26" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>86</v>
       </c>
-      <c r="G26" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="B27" t="s">
         <v>87</v>
-      </c>
-      <c r="B27" t="s">
-        <v>88</v>
       </c>
       <c r="C27">
         <v>120.961332865</v>
@@ -1885,21 +2036,24 @@
         <v>14.730764198999999</v>
       </c>
       <c r="E27" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F27" t="s">
         <v>89</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
+        <v>10</v>
+      </c>
+      <c r="H27" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>90</v>
       </c>
-      <c r="G27" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="B28" t="s">
         <v>91</v>
-      </c>
-      <c r="B28" t="s">
-        <v>92</v>
       </c>
       <c r="C28">
         <v>120.989964</v>
@@ -1908,21 +2062,24 @@
         <v>14.758217</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F28" t="s">
+        <v>92</v>
+      </c>
+      <c r="G28" t="s">
+        <v>10</v>
+      </c>
+      <c r="H28" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>93</v>
       </c>
-      <c r="G28" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="B29" t="s">
         <v>94</v>
-      </c>
-      <c r="B29" t="s">
-        <v>95</v>
       </c>
       <c r="C29">
         <v>120.971601795</v>
@@ -1931,21 +2088,24 @@
         <v>14.714030455</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F29" t="s">
+        <v>95</v>
+      </c>
+      <c r="G29" t="s">
         <v>96</v>
       </c>
-      <c r="G29" t="s">
+      <c r="H29" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>98</v>
-      </c>
       <c r="B30" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C30">
         <v>120.976297</v>
@@ -1954,21 +2114,24 @@
         <v>14.739205999999999</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F30" t="s">
+        <v>98</v>
+      </c>
+      <c r="G30" t="s">
+        <v>10</v>
+      </c>
+      <c r="H30" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>99</v>
       </c>
-      <c r="G30" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="B31" t="s">
         <v>100</v>
-      </c>
-      <c r="B31" t="s">
-        <v>101</v>
       </c>
       <c r="C31">
         <v>120.957392524</v>
@@ -1977,21 +2140,24 @@
         <v>14.73713757</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F31" t="s">
+        <v>101</v>
+      </c>
+      <c r="G31" t="s">
+        <v>10</v>
+      </c>
+      <c r="H31" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>102</v>
       </c>
-      <c r="G31" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="B32" t="s">
         <v>103</v>
-      </c>
-      <c r="B32" t="s">
-        <v>104</v>
       </c>
       <c r="C32">
         <v>120.910651571</v>
@@ -2000,21 +2166,24 @@
         <v>14.747199255</v>
       </c>
       <c r="E32" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F32" t="s">
         <v>105</v>
       </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
+        <v>10</v>
+      </c>
+      <c r="H32" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>106</v>
       </c>
-      <c r="G32" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="B33" t="s">
         <v>107</v>
-      </c>
-      <c r="B33" t="s">
-        <v>108</v>
       </c>
       <c r="C33">
         <v>120.93433752</v>
@@ -2023,21 +2192,24 @@
         <v>14.712042378</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F33" t="s">
+        <v>108</v>
+      </c>
+      <c r="G33" t="s">
+        <v>10</v>
+      </c>
+      <c r="H33" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>109</v>
       </c>
-      <c r="G33" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="B34" t="s">
         <v>110</v>
-      </c>
-      <c r="B34" t="s">
-        <v>111</v>
       </c>
       <c r="C34">
         <v>120.947287766</v>
@@ -2046,21 +2218,24 @@
         <v>14.709242875999999</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F34" t="s">
+        <v>111</v>
+      </c>
+      <c r="G34" t="s">
+        <v>96</v>
+      </c>
+      <c r="H34" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>112</v>
       </c>
-      <c r="G34" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="B35" t="s">
         <v>113</v>
-      </c>
-      <c r="B35" t="s">
-        <v>114</v>
       </c>
       <c r="C35" s="8">
         <v>120.04965799999999</v>
@@ -2069,21 +2244,24 @@
         <v>15.4323611</v>
       </c>
       <c r="E35" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F35" t="s">
         <v>115</v>
       </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>116</v>
       </c>
-      <c r="G35" t="s">
+      <c r="H35" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="B36" t="s">
         <v>118</v>
-      </c>
-      <c r="B36" t="s">
-        <v>119</v>
       </c>
       <c r="C36" s="8">
         <v>119.964872</v>
@@ -2092,21 +2270,24 @@
         <v>15.3912472</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F36" t="s">
+        <v>119</v>
+      </c>
+      <c r="G36" t="s">
+        <v>116</v>
+      </c>
+      <c r="H36" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>120</v>
       </c>
-      <c r="G36" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="B37" t="s">
         <v>121</v>
-      </c>
-      <c r="B37" t="s">
-        <v>122</v>
       </c>
       <c r="C37" s="8">
         <v>119.93927499999999</v>
@@ -2115,21 +2296,24 @@
         <v>15.392025</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F37" t="s">
+        <v>122</v>
+      </c>
+      <c r="G37" t="s">
+        <v>116</v>
+      </c>
+      <c r="H37" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>123</v>
       </c>
-      <c r="G37" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>124</v>
-      </c>
       <c r="B38" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C38" s="5">
         <v>121.571204481238</v>
@@ -2138,21 +2322,24 @@
         <v>15.736102406379599</v>
       </c>
       <c r="E38" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F38" t="s">
         <v>125</v>
       </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
         <v>126</v>
       </c>
-      <c r="G38" t="s">
+      <c r="H38" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>128</v>
-      </c>
       <c r="B39" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C39" s="4">
         <v>121.56879830839701</v>
@@ -2161,21 +2348,24 @@
         <v>15.7377462199136</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F39" t="s">
+        <v>128</v>
+      </c>
+      <c r="G39" t="s">
+        <v>126</v>
+      </c>
+      <c r="H39" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>129</v>
       </c>
-      <c r="G39" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>130</v>
-      </c>
       <c r="B40" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C40" s="6">
         <v>121.571215990216</v>
@@ -2184,21 +2374,24 @@
         <v>15.7362167081744</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F40" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G40" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+      <c r="H40" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B41" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C41" s="5">
         <v>120.912047614979</v>
@@ -2207,21 +2400,24 @@
         <v>15.587541681514001</v>
       </c>
       <c r="E41" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="F41" t="s">
         <v>132</v>
       </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>133</v>
       </c>
-      <c r="G41" t="s">
+      <c r="H41" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>135</v>
-      </c>
       <c r="B42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C42" s="5">
         <v>121.036631420061</v>
@@ -2230,21 +2426,24 @@
         <v>15.8274294236095</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F42" t="s">
+        <v>135</v>
+      </c>
+      <c r="G42" t="s">
+        <v>133</v>
+      </c>
+      <c r="H42" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>136</v>
       </c>
-      <c r="G42" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>137</v>
-      </c>
       <c r="B43" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C43" s="5">
         <v>120.925294789861</v>
@@ -2253,21 +2452,24 @@
         <v>16.104289899009</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F43" t="s">
+        <v>137</v>
+      </c>
+      <c r="G43" t="s">
+        <v>133</v>
+      </c>
+      <c r="H43" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>138</v>
       </c>
-      <c r="G43" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+      <c r="B44" t="s">
         <v>139</v>
-      </c>
-      <c r="B44" t="s">
-        <v>140</v>
       </c>
       <c r="C44">
         <v>121.57640615699999</v>
@@ -2276,21 +2478,24 @@
         <v>15.754688805000001</v>
       </c>
       <c r="E44" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F44" t="s">
         <v>141</v>
       </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
+        <v>126</v>
+      </c>
+      <c r="H44" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>142</v>
       </c>
-      <c r="G44" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+      <c r="B45" t="s">
         <v>143</v>
-      </c>
-      <c r="B45" t="s">
-        <v>144</v>
       </c>
       <c r="C45">
         <v>121.573426664</v>
@@ -2299,21 +2504,24 @@
         <v>15.756151685000001</v>
       </c>
       <c r="E45" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F45" t="s">
         <v>141</v>
       </c>
-      <c r="F45" t="s">
-        <v>142</v>
-      </c>
       <c r="G45" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+      <c r="H45" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>144</v>
+      </c>
+      <c r="B46" t="s">
         <v>145</v>
-      </c>
-      <c r="B46" t="s">
-        <v>146</v>
       </c>
       <c r="C46">
         <v>121.571451311</v>
@@ -2322,21 +2530,24 @@
         <v>15.758830742000001</v>
       </c>
       <c r="E46" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F46" t="s">
         <v>141</v>
       </c>
-      <c r="F46" t="s">
-        <v>142</v>
-      </c>
       <c r="G46" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+      <c r="H46" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>146</v>
+      </c>
+      <c r="B47" t="s">
         <v>147</v>
-      </c>
-      <c r="B47" t="s">
-        <v>148</v>
       </c>
       <c r="C47">
         <v>121.569645279</v>
@@ -2345,21 +2556,24 @@
         <v>15.761619101999999</v>
       </c>
       <c r="E47" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F47" t="s">
         <v>141</v>
       </c>
-      <c r="F47" t="s">
-        <v>142</v>
-      </c>
       <c r="G47" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+      <c r="H47" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>148</v>
+      </c>
+      <c r="B48" t="s">
         <v>149</v>
-      </c>
-      <c r="B48" t="s">
-        <v>150</v>
       </c>
       <c r="C48">
         <v>121.567089185</v>
@@ -2368,21 +2582,24 @@
         <v>15.765509977000001</v>
       </c>
       <c r="E48" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F48" t="s">
         <v>141</v>
       </c>
-      <c r="F48" t="s">
-        <v>142</v>
-      </c>
       <c r="G48" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+      <c r="H48" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>150</v>
+      </c>
+      <c r="B49" t="s">
         <v>151</v>
-      </c>
-      <c r="B49" t="s">
-        <v>152</v>
       </c>
       <c r="C49">
         <v>121.564035987</v>
@@ -2391,21 +2608,24 @@
         <v>15.770625347999999</v>
       </c>
       <c r="E49" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F49" t="s">
         <v>141</v>
       </c>
-      <c r="F49" t="s">
-        <v>142</v>
-      </c>
       <c r="G49" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+      <c r="H49" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>152</v>
+      </c>
+      <c r="B50" t="s">
         <v>153</v>
-      </c>
-      <c r="B50" t="s">
-        <v>154</v>
       </c>
       <c r="C50" s="5">
         <v>120.289995882707</v>
@@ -2414,21 +2634,24 @@
         <v>14.658051457130799</v>
       </c>
       <c r="E50" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="F50" t="s">
         <v>155</v>
       </c>
-      <c r="F50" t="s">
+      <c r="G50" t="s">
+        <v>20</v>
+      </c>
+      <c r="H50" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>156</v>
       </c>
-      <c r="G50" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+      <c r="B51" t="s">
         <v>157</v>
-      </c>
-      <c r="B51" t="s">
-        <v>158</v>
       </c>
       <c r="C51" s="5">
         <v>120.290826417983</v>
@@ -2437,21 +2660,24 @@
         <v>14.657213297262199</v>
       </c>
       <c r="E51" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="F51" t="s">
         <v>155</v>
       </c>
-      <c r="F51" t="s">
-        <v>156</v>
-      </c>
       <c r="G51" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="H51" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>158</v>
+      </c>
+      <c r="B52" t="s">
         <v>159</v>
-      </c>
-      <c r="B52" t="s">
-        <v>160</v>
       </c>
       <c r="C52" s="5">
         <v>120.289996471694</v>
@@ -2460,21 +2686,24 @@
         <v>14.658048102929101</v>
       </c>
       <c r="E52" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="F52" t="s">
         <v>155</v>
       </c>
-      <c r="F52" t="s">
-        <v>156</v>
-      </c>
       <c r="G52" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="H52" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>160</v>
+      </c>
+      <c r="B53" t="s">
         <v>161</v>
-      </c>
-      <c r="B53" t="s">
-        <v>162</v>
       </c>
       <c r="C53" s="5">
         <v>120.393044368543</v>
@@ -2483,21 +2712,24 @@
         <v>14.5875834844054</v>
       </c>
       <c r="E53" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="F53" t="s">
         <v>163</v>
       </c>
-      <c r="F53" t="s">
+      <c r="G53" t="s">
+        <v>20</v>
+      </c>
+      <c r="H53" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
         <v>164</v>
       </c>
-      <c r="G53" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+      <c r="B54" t="s">
         <v>165</v>
-      </c>
-      <c r="B54" t="s">
-        <v>166</v>
       </c>
       <c r="C54" s="5">
         <v>120.393566788637</v>
@@ -2506,21 +2738,24 @@
         <v>14.584987933351799</v>
       </c>
       <c r="E54" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="F54" t="s">
         <v>163</v>
       </c>
-      <c r="F54" t="s">
-        <v>164</v>
-      </c>
       <c r="G54" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="H54" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>166</v>
+      </c>
+      <c r="B55" t="s">
         <v>167</v>
-      </c>
-      <c r="B55" t="s">
-        <v>168</v>
       </c>
       <c r="C55" s="5">
         <v>120.393251528807</v>
@@ -2529,21 +2764,24 @@
         <v>14.5866362542688</v>
       </c>
       <c r="E55" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="F55" t="s">
         <v>163</v>
       </c>
-      <c r="F55" t="s">
-        <v>164</v>
-      </c>
       <c r="G55" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="H55" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>168</v>
+      </c>
+      <c r="B56" t="s">
         <v>169</v>
-      </c>
-      <c r="B56" t="s">
-        <v>170</v>
       </c>
       <c r="C56" s="5">
         <v>120.260877058319</v>
@@ -2552,21 +2790,24 @@
         <v>14.850257886405799</v>
       </c>
       <c r="E56" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="F56" t="s">
         <v>171</v>
       </c>
-      <c r="F56" t="s">
+      <c r="G56" t="s">
+        <v>116</v>
+      </c>
+      <c r="H56" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
         <v>172</v>
       </c>
-      <c r="G56" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+      <c r="B57" t="s">
         <v>173</v>
-      </c>
-      <c r="B57" t="s">
-        <v>174</v>
       </c>
       <c r="C57" s="5">
         <v>120.265306324416</v>
@@ -2575,21 +2816,24 @@
         <v>14.8482459497747</v>
       </c>
       <c r="E57" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="F57" t="s">
         <v>171</v>
       </c>
-      <c r="F57" t="s">
-        <v>172</v>
-      </c>
       <c r="G57" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="H57" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>174</v>
+      </c>
+      <c r="B58" t="s">
         <v>175</v>
-      </c>
-      <c r="B58" t="s">
-        <v>176</v>
       </c>
       <c r="C58" s="5">
         <v>120.266928115632</v>
@@ -2598,21 +2842,24 @@
         <v>14.8448071763053</v>
       </c>
       <c r="E58" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="F58" t="s">
         <v>171</v>
       </c>
-      <c r="F58" t="s">
-        <v>172</v>
-      </c>
       <c r="G58" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="H58" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>176</v>
+      </c>
+      <c r="B59" t="s">
         <v>177</v>
-      </c>
-      <c r="B59" t="s">
-        <v>178</v>
       </c>
       <c r="C59" s="5">
         <v>120.268177764257</v>
@@ -2621,21 +2868,24 @@
         <v>14.837649135260699</v>
       </c>
       <c r="E59" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="F59" t="s">
         <v>171</v>
       </c>
-      <c r="F59" t="s">
-        <v>172</v>
-      </c>
       <c r="G59" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="H59" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>178</v>
+      </c>
+      <c r="B60" t="s">
         <v>179</v>
-      </c>
-      <c r="B60" t="s">
-        <v>180</v>
       </c>
       <c r="C60">
         <v>119.959128007</v>
@@ -2644,21 +2894,24 @@
         <v>15.353569279</v>
       </c>
       <c r="E60" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F60" t="s">
         <v>181</v>
       </c>
-      <c r="F60" t="s">
+      <c r="G60" t="s">
+        <v>116</v>
+      </c>
+      <c r="H60" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
         <v>182</v>
       </c>
-      <c r="G60" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+      <c r="B61" t="s">
         <v>183</v>
-      </c>
-      <c r="B61" t="s">
-        <v>184</v>
       </c>
       <c r="C61">
         <v>119.96011704</v>
@@ -2667,21 +2920,24 @@
         <v>15.352973583000001</v>
       </c>
       <c r="E61" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F61" t="s">
         <v>181</v>
       </c>
-      <c r="F61" t="s">
-        <v>182</v>
-      </c>
       <c r="G61" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="H61" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>184</v>
+      </c>
+      <c r="B62" t="s">
         <v>185</v>
-      </c>
-      <c r="B62" t="s">
-        <v>186</v>
       </c>
       <c r="C62">
         <v>119.961026895</v>
@@ -2690,21 +2946,24 @@
         <v>15.352376037999999</v>
       </c>
       <c r="E62" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F62" t="s">
         <v>181</v>
       </c>
-      <c r="F62" t="s">
-        <v>182</v>
-      </c>
       <c r="G62" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="H62" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>186</v>
+      </c>
+      <c r="B63" t="s">
         <v>187</v>
-      </c>
-      <c r="B63" t="s">
-        <v>188</v>
       </c>
       <c r="C63">
         <v>119.962423058</v>
@@ -2713,21 +2972,24 @@
         <v>15.3512065</v>
       </c>
       <c r="E63" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F63" t="s">
         <v>181</v>
       </c>
-      <c r="F63" t="s">
-        <v>182</v>
-      </c>
       <c r="G63" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="H63" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>188</v>
+      </c>
+      <c r="B64" t="s">
         <v>189</v>
-      </c>
-      <c r="B64" t="s">
-        <v>190</v>
       </c>
       <c r="C64">
         <v>119.966261382</v>
@@ -2736,21 +2998,24 @@
         <v>15.345844067</v>
       </c>
       <c r="E64" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F64" t="s">
         <v>181</v>
       </c>
-      <c r="F64" t="s">
-        <v>182</v>
-      </c>
       <c r="G64" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="H64" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>190</v>
+      </c>
+      <c r="B65" t="s">
         <v>191</v>
-      </c>
-      <c r="B65" t="s">
-        <v>192</v>
       </c>
       <c r="C65">
         <v>119.96688833100001</v>
@@ -2759,21 +3024,24 @@
         <v>15.343492662999999</v>
       </c>
       <c r="E65" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F65" t="s">
         <v>181</v>
       </c>
-      <c r="F65" t="s">
-        <v>182</v>
-      </c>
       <c r="G65" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="H65" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>192</v>
+      </c>
+      <c r="B66" t="s">
         <v>193</v>
-      </c>
-      <c r="B66" t="s">
-        <v>194</v>
       </c>
       <c r="C66">
         <v>119.96636794600001</v>
@@ -2782,21 +3050,24 @@
         <v>15.324840833</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F66" t="s">
+        <v>194</v>
+      </c>
+      <c r="G66" t="s">
+        <v>116</v>
+      </c>
+      <c r="H66" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
         <v>195</v>
       </c>
-      <c r="G66" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+      <c r="B67" t="s">
         <v>196</v>
-      </c>
-      <c r="B67" t="s">
-        <v>197</v>
       </c>
       <c r="C67">
         <v>119.96848146799999</v>
@@ -2805,21 +3076,24 @@
         <v>15.322896883</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F67" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G67" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="H67" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>197</v>
+      </c>
+      <c r="B68" t="s">
         <v>198</v>
-      </c>
-      <c r="B68" t="s">
-        <v>199</v>
       </c>
       <c r="C68">
         <v>120.626182661</v>
@@ -2828,21 +3102,24 @@
         <v>14.932207213</v>
       </c>
       <c r="E68" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="F68" t="s">
         <v>200</v>
       </c>
-      <c r="F68" t="s">
+      <c r="G68" t="s">
+        <v>31</v>
+      </c>
+      <c r="H68" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
         <v>201</v>
       </c>
-      <c r="G68" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+      <c r="B69" t="s">
         <v>202</v>
-      </c>
-      <c r="B69" t="s">
-        <v>203</v>
       </c>
       <c r="C69">
         <v>120.613630942</v>
@@ -2851,21 +3128,24 @@
         <v>14.937574321</v>
       </c>
       <c r="E69" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="F69" t="s">
         <v>200</v>
       </c>
-      <c r="F69" t="s">
-        <v>201</v>
-      </c>
       <c r="G69" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="H69" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>203</v>
+      </c>
+      <c r="B70" t="s">
         <v>204</v>
-      </c>
-      <c r="B70" t="s">
-        <v>205</v>
       </c>
       <c r="C70">
         <v>120.684262745</v>
@@ -2874,21 +3154,24 @@
         <v>14.967223914</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F70" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G70" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="H70" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>205</v>
+      </c>
+      <c r="B71" t="s">
         <v>206</v>
-      </c>
-      <c r="B71" t="s">
-        <v>207</v>
       </c>
       <c r="C71">
         <v>120.718790322</v>
@@ -2897,21 +3180,24 @@
         <v>15.004767506</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F71" t="s">
+        <v>207</v>
+      </c>
+      <c r="G71" t="s">
+        <v>31</v>
+      </c>
+      <c r="H71" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
         <v>208</v>
       </c>
-      <c r="G71" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+      <c r="B72" t="s">
         <v>209</v>
-      </c>
-      <c r="B72" t="s">
-        <v>210</v>
       </c>
       <c r="C72">
         <v>120.694549384</v>
@@ -2920,21 +3206,24 @@
         <v>15.032860463</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F72" t="s">
+        <v>210</v>
+      </c>
+      <c r="G72" t="s">
+        <v>31</v>
+      </c>
+      <c r="H72" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
         <v>211</v>
       </c>
-      <c r="G72" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+      <c r="B73" t="s">
         <v>212</v>
-      </c>
-      <c r="B73" t="s">
-        <v>213</v>
       </c>
       <c r="C73">
         <v>120.730112981</v>
@@ -2943,21 +3232,24 @@
         <v>15.067992756000001</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F73" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G73" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="H73" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>213</v>
+      </c>
+      <c r="B74" t="s">
         <v>214</v>
-      </c>
-      <c r="B74" t="s">
-        <v>215</v>
       </c>
       <c r="C74">
         <v>120.607441448618</v>
@@ -2966,21 +3258,24 @@
         <v>15.1586840603666</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F74" t="s">
+        <v>215</v>
+      </c>
+      <c r="G74" t="s">
+        <v>31</v>
+      </c>
+      <c r="H74" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
         <v>216</v>
       </c>
-      <c r="G74" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
+      <c r="B75" t="s">
         <v>217</v>
-      </c>
-      <c r="B75" t="s">
-        <v>218</v>
       </c>
       <c r="C75">
         <v>120.607492263</v>
@@ -2989,21 +3284,24 @@
         <v>15.158772472000001</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F75" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G75" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="H75" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>218</v>
+      </c>
+      <c r="B76" t="s">
         <v>219</v>
-      </c>
-      <c r="B76" t="s">
-        <v>220</v>
       </c>
       <c r="C76">
         <v>120.5640676</v>
@@ -3012,15 +3310,21 @@
         <v>14.70028121</v>
       </c>
       <c r="E76" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="G76" t="s">
+        <v>20</v>
+      </c>
+      <c r="H76" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+      <c r="B77" t="s">
         <v>222</v>
-      </c>
-      <c r="B77" t="s">
-        <v>223</v>
       </c>
       <c r="C77">
         <v>120.56296067300001</v>
@@ -3029,15 +3333,21 @@
         <v>14.701563905</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+      <c r="G77" t="s">
+        <v>20</v>
+      </c>
+      <c r="H77" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>223</v>
+      </c>
+      <c r="B78" t="s">
         <v>224</v>
-      </c>
-      <c r="B78" t="s">
-        <v>225</v>
       </c>
       <c r="C78">
         <v>120.56159637</v>
@@ -3046,15 +3356,21 @@
         <v>14.702875676</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+      <c r="G78" t="s">
+        <v>20</v>
+      </c>
+      <c r="H78" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>225</v>
+      </c>
+      <c r="B79" t="s">
         <v>226</v>
-      </c>
-      <c r="B79" t="s">
-        <v>227</v>
       </c>
       <c r="C79">
         <v>120.63446133622701</v>
@@ -3063,18 +3379,21 @@
         <v>14.9657393746857</v>
       </c>
       <c r="E79" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G79" t="s">
+        <v>31</v>
+      </c>
+      <c r="H79" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
         <v>228</v>
       </c>
-      <c r="G79" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
+      <c r="B80" t="s">
         <v>229</v>
-      </c>
-      <c r="B80" t="s">
-        <v>230</v>
       </c>
       <c r="C80">
         <v>120.62529409</v>
@@ -3083,18 +3402,21 @@
         <v>14.965417552</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G80" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="H80" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>230</v>
+      </c>
+      <c r="B81" t="s">
         <v>231</v>
-      </c>
-      <c r="B81" t="s">
-        <v>232</v>
       </c>
       <c r="C81" s="9">
         <v>120.621467</v>
@@ -3103,18 +3425,21 @@
         <v>14.968876</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G81" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="H81" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>232</v>
+      </c>
+      <c r="B82" t="s">
         <v>233</v>
-      </c>
-      <c r="B82" t="s">
-        <v>234</v>
       </c>
       <c r="C82">
         <v>120.730040855</v>
@@ -3123,18 +3448,21 @@
         <v>14.883415004</v>
       </c>
       <c r="E82" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="G82" t="s">
+        <v>10</v>
+      </c>
+      <c r="H82" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
         <v>235</v>
       </c>
-      <c r="G82" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+      <c r="B83" t="s">
         <v>236</v>
-      </c>
-      <c r="B83" t="s">
-        <v>237</v>
       </c>
       <c r="C83">
         <v>120.740907299</v>
@@ -3143,18 +3471,21 @@
         <v>14.865882151999999</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G83" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H83" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>237</v>
+      </c>
+      <c r="B84" t="s">
         <v>238</v>
-      </c>
-      <c r="B84" t="s">
-        <v>239</v>
       </c>
       <c r="C84">
         <v>120.739283892</v>
@@ -3163,18 +3494,21 @@
         <v>14.83992632</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G84" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H84" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>239</v>
+      </c>
+      <c r="B85" t="s">
         <v>240</v>
-      </c>
-      <c r="B85" t="s">
-        <v>241</v>
       </c>
       <c r="C85">
         <v>120.73004629099999</v>
@@ -3183,18 +3517,21 @@
         <v>14.816397939</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G85" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H85" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>241</v>
+      </c>
+      <c r="B86" t="s">
         <v>242</v>
-      </c>
-      <c r="B86" t="s">
-        <v>243</v>
       </c>
       <c r="C86">
         <v>120.82232625899999</v>
@@ -3203,18 +3540,21 @@
         <v>14.828111932000001</v>
       </c>
       <c r="E86" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="G86" t="s">
+        <v>10</v>
+      </c>
+      <c r="H86" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
         <v>244</v>
       </c>
-      <c r="G86" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
+      <c r="B87" t="s">
         <v>245</v>
-      </c>
-      <c r="B87" t="s">
-        <v>246</v>
       </c>
       <c r="C87">
         <v>120.83100967</v>
@@ -3223,18 +3563,21 @@
         <v>14.832484425000001</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G87" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H87" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>246</v>
+      </c>
+      <c r="B88" t="s">
         <v>247</v>
-      </c>
-      <c r="B88" t="s">
-        <v>248</v>
       </c>
       <c r="C88">
         <v>120.833801079</v>
@@ -3243,18 +3586,21 @@
         <v>14.836052636</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G88" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H88" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>248</v>
+      </c>
+      <c r="B89" t="s">
         <v>249</v>
-      </c>
-      <c r="B89" t="s">
-        <v>250</v>
       </c>
       <c r="C89">
         <v>121.56789999999999</v>
@@ -3263,18 +3609,21 @@
         <v>15.756</v>
       </c>
       <c r="E89" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G89" t="s">
+        <v>126</v>
+      </c>
+      <c r="H89" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
         <v>251</v>
       </c>
-      <c r="G89" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
+      <c r="B90" t="s">
         <v>252</v>
-      </c>
-      <c r="B90" t="s">
-        <v>253</v>
       </c>
       <c r="C90">
         <v>121.5656</v>
@@ -3283,18 +3632,21 @@
         <v>15.7597</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G90" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+      <c r="H90" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>253</v>
+      </c>
+      <c r="B91" t="s">
         <v>254</v>
-      </c>
-      <c r="B91" t="s">
-        <v>255</v>
       </c>
       <c r="C91">
         <v>121.5616</v>
@@ -3303,18 +3655,21 @@
         <v>15.7677</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G91" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+      <c r="H91" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>255</v>
+      </c>
+      <c r="B92" t="s">
         <v>256</v>
-      </c>
-      <c r="B92" t="s">
-        <v>257</v>
       </c>
       <c r="C92">
         <v>121.55629999999999</v>
@@ -3323,18 +3678,21 @@
         <v>15.7698</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G92" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+      <c r="H92" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>257</v>
+      </c>
+      <c r="B93" t="s">
         <v>258</v>
-      </c>
-      <c r="B93" t="s">
-        <v>259</v>
       </c>
       <c r="C93">
         <v>120.5330556</v>
@@ -3343,18 +3701,21 @@
         <v>14.94166667</v>
       </c>
       <c r="E93" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="G93" t="s">
+        <v>31</v>
+      </c>
+      <c r="H93" s="12" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
         <v>260</v>
       </c>
-      <c r="G93" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
+      <c r="B94" t="s">
         <v>261</v>
-      </c>
-      <c r="B94" t="s">
-        <v>262</v>
       </c>
       <c r="C94">
         <v>120.4772222</v>
@@ -3363,18 +3724,21 @@
         <v>14.977499999999999</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G94" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="H94" s="12" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>262</v>
+      </c>
+      <c r="B95" t="s">
         <v>263</v>
-      </c>
-      <c r="B95" t="s">
-        <v>264</v>
       </c>
       <c r="C95">
         <v>120.4686111</v>
@@ -3383,14 +3747,17 @@
         <v>15.014722219999999</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G95" t="s">
-        <v>32</v>
+        <v>31</v>
+      </c>
+      <c r="H95" s="12" t="s">
+        <v>259</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G92" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:G95" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
